--- a/03_model/inputs/stock_on_hand_2026-05-13.xlsx
+++ b/03_model/inputs/stock_on_hand_2026-05-13.xlsx
@@ -246,7 +246,7 @@
     <t>1 of 12</t>
   </si>
   <si>
-    <t>Generated 13/05/2026 at 13:32:00</t>
+    <t>Generated 13/05/2026 at 16:05:01</t>
   </si>
   <si>
     <t>9313711001015</t>
@@ -2605,21 +2605,21 @@
         <v>24.4859</v>
       </c>
       <c r="I9" s="21">
-        <v>19.207</v>
+        <v>17.62</v>
       </c>
       <c r="J9" s="21"/>
       <c r="K9" s="21">
-        <v>0.784410619989463</v>
+        <v>0.719597809351504</v>
       </c>
       <c r="L9" s="21" t="s">
         <v>22</v>
       </c>
       <c r="M9" s="21">
-        <v>46.0968</v>
+        <v>42.288</v>
       </c>
       <c r="N9" s="21"/>
       <c r="O9" s="21">
-        <v>76.63593</v>
+        <v>70.3038</v>
       </c>
       <c r="P9" s="21"/>
       <c r="Q9" s="21">
@@ -2651,21 +2651,21 @@
         <v>140.5392</v>
       </c>
       <c r="I10" s="26">
-        <v>53.9</v>
+        <v>51.681</v>
       </c>
       <c r="J10" s="26"/>
       <c r="K10" s="26">
-        <v>0.383522888987556</v>
+        <v>0.367733699921445</v>
       </c>
       <c r="L10" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M10" s="26">
-        <v>80.85</v>
+        <v>77.5215</v>
       </c>
       <c r="N10" s="26"/>
       <c r="O10" s="26">
-        <v>144.991</v>
+        <v>139.02189</v>
       </c>
       <c r="P10" s="26"/>
       <c r="Q10" s="26">
@@ -2695,21 +2695,21 @@
         <v>1775.8</v>
       </c>
       <c r="I11" s="31">
-        <v>-1431</v>
+        <v>-1577</v>
       </c>
       <c r="J11" s="31"/>
       <c r="K11" s="31">
-        <v>-0.805833990314225</v>
+        <v>-0.888050456132447</v>
       </c>
       <c r="L11" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M11" s="31">
-        <v>-8.586</v>
+        <v>-9.462</v>
       </c>
       <c r="N11" s="31"/>
       <c r="O11" s="31">
-        <v>-14.29569</v>
+        <v>-15.75423</v>
       </c>
       <c r="P11" s="31"/>
       <c r="Q11" s="31">
@@ -2741,21 +2741,21 @@
         <v>30.9767</v>
       </c>
       <c r="I12" s="26">
-        <v>18.536</v>
+        <v>17.975</v>
       </c>
       <c r="J12" s="26"/>
       <c r="K12" s="26">
-        <v>0.598385237936901</v>
+        <v>0.580274851743407</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M12" s="26">
-        <v>101.948</v>
+        <v>98.8625</v>
       </c>
       <c r="N12" s="26"/>
       <c r="O12" s="26">
-        <v>170.34584</v>
+        <v>165.19025</v>
       </c>
       <c r="P12" s="26"/>
       <c r="Q12" s="26">
@@ -2833,21 +2833,21 @@
         <v>25.707</v>
       </c>
       <c r="I14" s="26">
-        <v>17.689</v>
+        <v>14.52</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26">
-        <v>0.68810051736881</v>
+        <v>0.564826700898588</v>
       </c>
       <c r="L14" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="26">
-        <v>51.2981</v>
+        <v>42.108</v>
       </c>
       <c r="N14" s="26"/>
       <c r="O14" s="26">
-        <v>88.26811</v>
+        <v>72.4548</v>
       </c>
       <c r="P14" s="26"/>
       <c r="Q14" s="26">
@@ -2877,28 +2877,28 @@
         <v>3.5</v>
       </c>
       <c r="I15" s="31">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" s="31"/>
       <c r="K15" s="31">
-        <v>4.85714285714286</v>
+        <v>4.28571428571429</v>
       </c>
       <c r="L15" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M15" s="31">
-        <v>45.05</v>
+        <v>39.75</v>
       </c>
       <c r="N15" s="31"/>
       <c r="O15" s="31">
-        <v>59.5</v>
+        <v>52.5</v>
       </c>
       <c r="P15" s="31"/>
       <c r="Q15" s="31">
         <v>24.29</v>
       </c>
       <c r="R15" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S15" s="31">
         <v>0</v>
@@ -3011,21 +3011,21 @@
         <v>67.5889</v>
       </c>
       <c r="I18" s="26">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J18" s="26"/>
       <c r="K18" s="26">
-        <v>0.340292562832063</v>
+        <v>0.325497234013277</v>
       </c>
       <c r="L18" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M18" s="26">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N18" s="26"/>
       <c r="O18" s="26">
-        <v>114.77</v>
+        <v>109.78</v>
       </c>
       <c r="P18" s="26"/>
       <c r="Q18" s="26">
@@ -3235,28 +3235,28 @@
         <v>13.7667</v>
       </c>
       <c r="I23" s="31">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J23" s="31"/>
       <c r="K23" s="31">
-        <v>0.944307640901596</v>
+        <v>0.79902954230135</v>
       </c>
       <c r="L23" s="31" t="s">
         <v>55</v>
       </c>
       <c r="M23" s="31">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N23" s="31"/>
       <c r="O23" s="31">
-        <v>23.27</v>
+        <v>19.69</v>
       </c>
       <c r="P23" s="31"/>
       <c r="Q23" s="31">
         <v>44.13</v>
       </c>
       <c r="R23" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S23" s="31">
         <v>0</v>
@@ -3615,21 +3615,21 @@
         <v>132.2222</v>
       </c>
       <c r="I35" s="26">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J35" s="26"/>
       <c r="K35" s="26">
-        <v>0.181512635548342</v>
+        <v>0.128571450180076</v>
       </c>
       <c r="L35" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M35" s="26">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N35" s="26"/>
       <c r="O35" s="26">
-        <v>160.56</v>
+        <v>113.73</v>
       </c>
       <c r="P35" s="26"/>
       <c r="Q35" s="26">
@@ -4259,21 +4259,21 @@
         <v>20.9988</v>
       </c>
       <c r="I49" s="26">
-        <v>27.635</v>
+        <v>26.749</v>
       </c>
       <c r="J49" s="26"/>
       <c r="K49" s="26">
-        <v>1.31602758252853</v>
+        <v>1.27383469531592</v>
       </c>
       <c r="L49" s="26" t="s">
         <v>78</v>
       </c>
       <c r="M49" s="26">
-        <v>71.060639</v>
+        <v>68.7823786</v>
       </c>
       <c r="N49" s="26"/>
       <c r="O49" s="26">
-        <v>137.89865</v>
+        <v>133.47751</v>
       </c>
       <c r="P49" s="26"/>
       <c r="Q49" s="26">
@@ -4303,28 +4303,28 @@
         <v>6.3</v>
       </c>
       <c r="I50" s="31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="31"/>
       <c r="K50" s="31">
-        <v>0.158730158730159</v>
+        <v>0</v>
       </c>
       <c r="L50" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M50" s="31">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N50" s="31"/>
       <c r="O50" s="31">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="P50" s="31"/>
       <c r="Q50" s="31">
         <v>39.92</v>
       </c>
       <c r="R50" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S50" s="31">
         <v>0</v>
@@ -4730,28 +4730,28 @@
         <v>22.7889</v>
       </c>
       <c r="I64" s="31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J64" s="31"/>
       <c r="K64" s="31">
-        <v>0.482691134719096</v>
+        <v>0.438810122471905</v>
       </c>
       <c r="L64" s="31" t="s">
         <v>55</v>
       </c>
       <c r="M64" s="31">
-        <v>24.2</v>
+        <v>22</v>
       </c>
       <c r="N64" s="31"/>
       <c r="O64" s="31">
-        <v>42.9</v>
+        <v>39</v>
       </c>
       <c r="P64" s="31"/>
       <c r="Q64" s="31">
         <v>43.59</v>
       </c>
       <c r="R64" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S64" s="31">
         <v>0</v>
@@ -4908,21 +4908,21 @@
         <v>66.1111</v>
       </c>
       <c r="I68" s="31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J68" s="31"/>
       <c r="K68" s="31">
-        <v>0.211764741473066</v>
+        <v>0.181512635548342</v>
       </c>
       <c r="L68" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M68" s="31">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N68" s="31"/>
       <c r="O68" s="31">
-        <v>55.86</v>
+        <v>47.88</v>
       </c>
       <c r="P68" s="31"/>
       <c r="Q68" s="31">
@@ -4954,21 +4954,21 @@
         <v>33.4196</v>
       </c>
       <c r="I69" s="26">
-        <v>73.035</v>
+        <v>70.604</v>
       </c>
       <c r="J69" s="26"/>
       <c r="K69" s="26">
-        <v>2.18539419981089</v>
+        <v>2.11265245544531</v>
       </c>
       <c r="L69" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M69" s="26">
-        <v>124.1595</v>
+        <v>120.0268</v>
       </c>
       <c r="N69" s="26"/>
       <c r="O69" s="26">
-        <v>138.7665</v>
+        <v>134.1476</v>
       </c>
       <c r="P69" s="26"/>
       <c r="Q69" s="26">
@@ -5000,21 +5000,21 @@
         <v>38.7676</v>
       </c>
       <c r="I70" s="31">
-        <v>19.525</v>
+        <v>15.444</v>
       </c>
       <c r="J70" s="31"/>
       <c r="K70" s="31">
-        <v>0.503642216696417</v>
+        <v>0.398373899854518</v>
       </c>
       <c r="L70" s="31" t="s">
         <v>55</v>
       </c>
       <c r="M70" s="31">
-        <v>29.2875</v>
+        <v>23.166</v>
       </c>
       <c r="N70" s="31"/>
       <c r="O70" s="31">
-        <v>52.52225</v>
+        <v>41.54436</v>
       </c>
       <c r="P70" s="31"/>
       <c r="Q70" s="31">
@@ -5046,21 +5046,21 @@
         <v>41.8732</v>
       </c>
       <c r="I71" s="26">
-        <v>16.348</v>
+        <v>11.669</v>
       </c>
       <c r="J71" s="26"/>
       <c r="K71" s="26">
-        <v>0.390416782094514</v>
+        <v>0.278674665418454</v>
       </c>
       <c r="L71" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M71" s="26">
-        <v>32.696</v>
+        <v>23.338</v>
       </c>
       <c r="N71" s="26"/>
       <c r="O71" s="26">
-        <v>81.57652</v>
+        <v>58.22831</v>
       </c>
       <c r="P71" s="26"/>
       <c r="Q71" s="26">
@@ -5092,28 +5092,28 @@
         <v>10257.6</v>
       </c>
       <c r="I72" s="31">
-        <v>-15941</v>
+        <v>-17793</v>
       </c>
       <c r="J72" s="31"/>
       <c r="K72" s="31">
-        <v>-1.55406722820153</v>
+        <v>-1.734616284511</v>
       </c>
       <c r="L72" s="31" t="s">
         <v>58</v>
       </c>
       <c r="M72" s="31">
-        <v>-63.764</v>
+        <v>-71.172</v>
       </c>
       <c r="N72" s="31"/>
       <c r="O72" s="31">
-        <v>-111.42759</v>
+        <v>-124.37307</v>
       </c>
       <c r="P72" s="31"/>
       <c r="Q72" s="31">
         <v>42.78</v>
       </c>
       <c r="R72" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S72" s="31">
         <v>0</v>
@@ -5138,21 +5138,21 @@
         <v>33.9631</v>
       </c>
       <c r="I73" s="26">
-        <v>25.986</v>
+        <v>25.14</v>
       </c>
       <c r="J73" s="26"/>
       <c r="K73" s="26">
-        <v>0.765124502769182</v>
+        <v>0.740215115816872</v>
       </c>
       <c r="L73" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M73" s="26">
-        <v>103.944</v>
+        <v>100.56</v>
       </c>
       <c r="N73" s="26"/>
       <c r="O73" s="26">
-        <v>181.64214</v>
+        <v>175.7286</v>
       </c>
       <c r="P73" s="26"/>
       <c r="Q73" s="26">
@@ -5182,21 +5182,21 @@
         <v>7.3889</v>
       </c>
       <c r="I74" s="31">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J74" s="31"/>
       <c r="K74" s="31">
-        <v>1.75939585053256</v>
+        <v>0.947366996440607</v>
       </c>
       <c r="L74" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M74" s="31">
-        <v>45.5</v>
+        <v>24.5</v>
       </c>
       <c r="N74" s="31"/>
       <c r="O74" s="31">
-        <v>58.5</v>
+        <v>31.5</v>
       </c>
       <c r="P74" s="31"/>
       <c r="Q74" s="31">
@@ -6319,21 +6319,21 @@
         <v>32.5111</v>
       </c>
       <c r="I104" s="31">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="J104" s="31"/>
       <c r="K104" s="31">
-        <v>-0.707450686073372</v>
+        <v>-0.738209411554823</v>
       </c>
       <c r="L104" s="31" t="s">
         <v>78</v>
       </c>
       <c r="M104" s="31">
-        <v>-31.05</v>
+        <v>-32.4</v>
       </c>
       <c r="N104" s="31"/>
       <c r="O104" s="31">
-        <v>-41.4</v>
+        <v>-43.2</v>
       </c>
       <c r="P104" s="31"/>
       <c r="Q104" s="31">
@@ -6744,21 +6744,21 @@
         <v>22.5961</v>
       </c>
       <c r="I118" s="31">
-        <v>20.037</v>
+        <v>19.17</v>
       </c>
       <c r="J118" s="31"/>
       <c r="K118" s="31">
-        <v>0.886745942883949</v>
+        <v>0.848376489748231</v>
       </c>
       <c r="L118" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M118" s="31">
-        <v>60.111</v>
+        <v>57.51</v>
       </c>
       <c r="N118" s="31"/>
       <c r="O118" s="31">
-        <v>103.99203</v>
+        <v>99.4923</v>
       </c>
       <c r="P118" s="31"/>
       <c r="Q118" s="31">
@@ -6790,21 +6790,21 @@
         <v>63.6222</v>
       </c>
       <c r="I119" s="26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J119" s="26"/>
       <c r="K119" s="26">
-        <v>0.502969089405899</v>
+        <v>0.471533521318031</v>
       </c>
       <c r="L119" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M119" s="26">
-        <v>57.6</v>
+        <v>54</v>
       </c>
       <c r="N119" s="26"/>
       <c r="O119" s="26">
-        <v>102.4</v>
+        <v>96</v>
       </c>
       <c r="P119" s="26"/>
       <c r="Q119" s="26">
@@ -6836,21 +6836,21 @@
         <v>33.3462</v>
       </c>
       <c r="I120" s="31">
-        <v>41.418</v>
+        <v>39.989</v>
       </c>
       <c r="J120" s="31"/>
       <c r="K120" s="31">
-        <v>1.24206056462206</v>
+        <v>1.19920710605706</v>
       </c>
       <c r="L120" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M120" s="31">
-        <v>82.836</v>
+        <v>79.978</v>
       </c>
       <c r="N120" s="31"/>
       <c r="O120" s="31">
-        <v>165.25782</v>
+        <v>159.55611</v>
       </c>
       <c r="P120" s="31"/>
       <c r="Q120" s="31">
@@ -7106,21 +7106,21 @@
         <v>2250.3</v>
       </c>
       <c r="I126" s="31">
-        <v>-907</v>
+        <v>-1279</v>
       </c>
       <c r="J126" s="31"/>
       <c r="K126" s="31">
-        <v>-0.403057370128427</v>
+        <v>-0.568368661956184</v>
       </c>
       <c r="L126" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M126" s="31">
-        <v>-12.0933031</v>
+        <v>-17.0532907</v>
       </c>
       <c r="N126" s="31"/>
       <c r="O126" s="31">
-        <v>-20.57983</v>
+        <v>-29.02051</v>
       </c>
       <c r="P126" s="31"/>
       <c r="Q126" s="31">
@@ -7240,21 +7240,21 @@
         <v>16.604</v>
       </c>
       <c r="I129" s="26">
-        <v>4.029</v>
+        <v>3.373</v>
       </c>
       <c r="J129" s="26"/>
       <c r="K129" s="26">
-        <v>0.242652372922187</v>
+        <v>0.20314382076608</v>
       </c>
       <c r="L129" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M129" s="26">
-        <v>40.29</v>
+        <v>33.73</v>
       </c>
       <c r="N129" s="26"/>
       <c r="O129" s="26">
-        <v>68.45271</v>
+        <v>57.30727</v>
       </c>
       <c r="P129" s="26"/>
       <c r="Q129" s="26">
@@ -7487,21 +7487,21 @@
         <v>12.5222</v>
       </c>
       <c r="I139" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J139" s="26"/>
       <c r="K139" s="26">
-        <v>0.399290859433646</v>
+        <v>0.239574515660188</v>
       </c>
       <c r="L139" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M139" s="26">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="N139" s="26"/>
       <c r="O139" s="26">
-        <v>29.95</v>
+        <v>17.97</v>
       </c>
       <c r="P139" s="26"/>
       <c r="Q139" s="26">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="T142" s="32"/>
     </row>
-    <row r="143" spans="1:20" ht="17.4528" customHeight="1">
+    <row r="143" spans="1:20" ht="26.1792" customHeight="1">
       <c r="A143" s="23" t="s">
         <v>295</v>
       </c>
@@ -7667,21 +7667,21 @@
         <v>5937.5</v>
       </c>
       <c r="I143" s="26">
-        <v>-9759.5</v>
+        <v>-10855.5</v>
       </c>
       <c r="J143" s="26"/>
       <c r="K143" s="26">
-        <v>-1.64370526315789</v>
+        <v>-1.82829473684211</v>
       </c>
       <c r="L143" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M143" s="26">
-        <v>-39.038</v>
+        <v>-43.422</v>
       </c>
       <c r="N143" s="26"/>
       <c r="O143" s="26">
-        <v>-68.218905</v>
+        <v>-75.879945</v>
       </c>
       <c r="P143" s="26"/>
       <c r="Q143" s="26">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="T148" s="32"/>
     </row>
-    <row r="149" spans="1:20" ht="17.4528" customHeight="1">
+    <row r="149" spans="1:20" ht="16.7256" customHeight="1">
       <c r="A149" s="23" t="s">
         <v>313</v>
       </c>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="T149" s="27"/>
     </row>
-    <row r="150" spans="1:20" ht="16.7256" customHeight="1">
+    <row r="150" spans="1:20" ht="17.4528" customHeight="1">
       <c r="A150" s="28" t="s">
         <v>317</v>
       </c>
@@ -8081,21 +8081,21 @@
         <v>11.5111</v>
       </c>
       <c r="I152" s="31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J152" s="31"/>
       <c r="K152" s="31">
-        <v>0.173745341453032</v>
+        <v>0.0868726707265161</v>
       </c>
       <c r="L152" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M152" s="31">
-        <v>5.22</v>
+        <v>2.61</v>
       </c>
       <c r="N152" s="31"/>
       <c r="O152" s="31">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="P152" s="31"/>
       <c r="Q152" s="31">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="T152" s="32"/>
     </row>
-    <row r="153" spans="1:20" ht="26.1792" customHeight="1">
+    <row r="153" spans="1:20" ht="25.452" customHeight="1">
       <c r="A153" s="23" t="s">
         <v>326</v>
       </c>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="T153" s="27"/>
     </row>
-    <row r="154" spans="1:20" ht="16.7256" customHeight="1">
+    <row r="154" spans="1:20" ht="17.4528" customHeight="1">
       <c r="A154" s="28" t="s">
         <v>328</v>
       </c>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="T157" s="27"/>
     </row>
-    <row r="158" spans="1:20" ht="14.544" customHeight="1"/>
+    <row r="158" spans="1:20" ht="5.8176" customHeight="1"/>
     <row r="159" spans="1:20" ht="16.7256" customHeight="1">
       <c r="A159" s="34" t="s">
         <v>72</v>
@@ -8552,21 +8552,21 @@
         <v>127.4</v>
       </c>
       <c r="I167" s="26">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J167" s="26"/>
       <c r="K167" s="26">
-        <v>0.769230769230769</v>
+        <v>0.745682888540031</v>
       </c>
       <c r="L167" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M167" s="26">
-        <v>228.6634</v>
+        <v>221.6635</v>
       </c>
       <c r="N167" s="26"/>
       <c r="O167" s="26">
-        <v>391.02</v>
+        <v>379.05</v>
       </c>
       <c r="P167" s="26"/>
       <c r="Q167" s="26">
@@ -8688,28 +8688,28 @@
         <v>4.2</v>
       </c>
       <c r="I170" s="31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J170" s="31"/>
       <c r="K170" s="31">
-        <v>1.42857142857143</v>
+        <v>0.476190476190476</v>
       </c>
       <c r="L170" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M170" s="31">
-        <v>10.9998</v>
+        <v>3.6666</v>
       </c>
       <c r="N170" s="31"/>
       <c r="O170" s="31">
-        <v>19.74</v>
+        <v>6.58</v>
       </c>
       <c r="P170" s="31"/>
       <c r="Q170" s="31">
         <v>44.28</v>
       </c>
       <c r="R170" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S170" s="31">
         <v>0</v>
@@ -9555,21 +9555,21 @@
         <v>76.4591</v>
       </c>
       <c r="I194" s="45">
-        <v>53.405</v>
+        <v>50.77</v>
       </c>
       <c r="J194" s="45"/>
       <c r="K194" s="45">
-        <v>0.698478009811782</v>
+        <v>0.664015140120666</v>
       </c>
       <c r="L194" s="45" t="s">
         <v>22</v>
       </c>
       <c r="M194" s="45">
-        <v>240.3225</v>
+        <v>228.465</v>
       </c>
       <c r="N194" s="45"/>
       <c r="O194" s="45">
-        <v>405.34395</v>
+        <v>385.3443</v>
       </c>
       <c r="P194" s="45"/>
       <c r="Q194" s="45">
@@ -9599,21 +9599,21 @@
         <v>42.1855</v>
       </c>
       <c r="I195" s="26">
-        <v>33.04</v>
+        <v>31.265</v>
       </c>
       <c r="J195" s="26"/>
       <c r="K195" s="26">
-        <v>0.783207500207417</v>
+        <v>0.741131431416008</v>
       </c>
       <c r="L195" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M195" s="26">
-        <v>148.68</v>
+        <v>140.6925</v>
       </c>
       <c r="N195" s="26"/>
       <c r="O195" s="26">
-        <v>250.7736</v>
+        <v>237.30135</v>
       </c>
       <c r="P195" s="26"/>
       <c r="Q195" s="26">
@@ -9733,28 +9733,28 @@
         <v>0.8791</v>
       </c>
       <c r="I198" s="31">
-        <v>0.499</v>
+        <v>0.403</v>
       </c>
       <c r="J198" s="31"/>
       <c r="K198" s="31">
-        <v>0.567625981117052</v>
+        <v>0.458423387555454</v>
       </c>
       <c r="L198" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M198" s="31">
-        <v>12.475</v>
+        <v>10.075</v>
       </c>
       <c r="N198" s="31"/>
       <c r="O198" s="31">
-        <v>19.95501</v>
+        <v>16.11597</v>
       </c>
       <c r="P198" s="31"/>
       <c r="Q198" s="31">
         <v>37.48</v>
       </c>
       <c r="R198" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S198" s="31">
         <v>0</v>
@@ -10181,21 +10181,21 @@
         <v>129.8889</v>
       </c>
       <c r="I208" s="31">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J208" s="31"/>
       <c r="K208" s="31">
-        <v>0.600513207826073</v>
+        <v>0.58511543326643</v>
       </c>
       <c r="L208" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M208" s="31">
-        <v>91.0026</v>
+        <v>88.6692</v>
       </c>
       <c r="N208" s="31"/>
       <c r="O208" s="31">
-        <v>155.22</v>
+        <v>151.24</v>
       </c>
       <c r="P208" s="31"/>
       <c r="Q208" s="31">
@@ -10225,21 +10225,21 @@
         <v>38.3444</v>
       </c>
       <c r="I209" s="26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J209" s="26"/>
       <c r="K209" s="26">
-        <v>0.365111985061704</v>
+        <v>0.312953130052889</v>
       </c>
       <c r="L209" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M209" s="26">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="N209" s="26"/>
       <c r="O209" s="26">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P209" s="26"/>
       <c r="Q209" s="26">
@@ -10762,28 +10762,28 @@
         <v>9.6444</v>
       </c>
       <c r="I225" s="26">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J225" s="26"/>
       <c r="K225" s="26">
-        <v>-0.311061341296504</v>
+        <v>-0.414748455062005</v>
       </c>
       <c r="L225" s="26" t="s">
         <v>78</v>
       </c>
       <c r="M225" s="26">
-        <v>-9.99</v>
+        <v>-13.32</v>
       </c>
       <c r="N225" s="26"/>
       <c r="O225" s="26">
-        <v>-16.65</v>
+        <v>-22.2</v>
       </c>
       <c r="P225" s="26"/>
       <c r="Q225" s="26">
         <v>40</v>
       </c>
       <c r="R225" s="26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S225" s="26">
         <v>0</v>
@@ -11124,21 +11124,21 @@
         <v>16.0101</v>
       </c>
       <c r="I233" s="26">
-        <v>-25419.145</v>
+        <v>-25419.902</v>
       </c>
       <c r="J233" s="26"/>
       <c r="K233" s="26">
-        <v>-1587.6943304539</v>
+        <v>-1587.74161310673</v>
       </c>
       <c r="L233" s="26" t="s">
         <v>187</v>
       </c>
       <c r="M233" s="26">
-        <v>-40670.632</v>
+        <v>-40671.8432</v>
       </c>
       <c r="N233" s="26"/>
       <c r="O233" s="26">
-        <v>-76003.24355</v>
+        <v>-76005.50698</v>
       </c>
       <c r="P233" s="26"/>
       <c r="Q233" s="26">
@@ -11168,28 +11168,28 @@
         <v>8.7889</v>
       </c>
       <c r="I234" s="31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J234" s="31"/>
       <c r="K234" s="31">
-        <v>0.568899407206818</v>
+        <v>0.455119525765454</v>
       </c>
       <c r="L234" s="31" t="s">
         <v>55</v>
       </c>
       <c r="M234" s="31">
-        <v>13.75</v>
+        <v>11</v>
       </c>
       <c r="N234" s="31"/>
       <c r="O234" s="31">
-        <v>23.95</v>
+        <v>19.16</v>
       </c>
       <c r="P234" s="31"/>
       <c r="Q234" s="31">
         <v>42.59</v>
       </c>
       <c r="R234" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S234" s="31">
         <v>0</v>
@@ -11214,21 +11214,21 @@
         <v>96.8333</v>
       </c>
       <c r="I235" s="26">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J235" s="26"/>
       <c r="K235" s="26">
-        <v>0.629948581737894</v>
+        <v>0.609294529877635</v>
       </c>
       <c r="L235" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M235" s="26">
-        <v>70.15</v>
+        <v>67.85</v>
       </c>
       <c r="N235" s="26"/>
       <c r="O235" s="26">
-        <v>131.15</v>
+        <v>126.85</v>
       </c>
       <c r="P235" s="26"/>
       <c r="Q235" s="26">
@@ -11260,21 +11260,21 @@
         <v>23.1257</v>
       </c>
       <c r="I236" s="31">
-        <v>8.618</v>
+        <v>7.4</v>
       </c>
       <c r="J236" s="31"/>
       <c r="K236" s="31">
-        <v>0.372658989781931</v>
+        <v>0.319990313806717</v>
       </c>
       <c r="L236" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M236" s="31">
-        <v>47.399</v>
+        <v>40.7</v>
       </c>
       <c r="N236" s="31"/>
       <c r="O236" s="31">
-        <v>82.64662</v>
+        <v>70.966</v>
       </c>
       <c r="P236" s="31"/>
       <c r="Q236" s="31">
@@ -11915,21 +11915,21 @@
         <v>46.0826</v>
       </c>
       <c r="I255" s="26">
-        <v>-13.427</v>
+        <v>-17.033</v>
       </c>
       <c r="J255" s="26"/>
       <c r="K255" s="26">
-        <v>-0.291368108570263</v>
+        <v>-0.369618901711275</v>
       </c>
       <c r="L255" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M255" s="26">
-        <v>-53.708</v>
+        <v>-68.132</v>
       </c>
       <c r="N255" s="26"/>
       <c r="O255" s="26">
-        <v>-89.9609</v>
+        <v>-114.1211</v>
       </c>
       <c r="P255" s="26"/>
       <c r="Q255" s="26">
@@ -12179,21 +12179,21 @@
         <v>17.5778</v>
       </c>
       <c r="I261" s="26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J261" s="26"/>
       <c r="K261" s="26">
-        <v>0.96712899225159</v>
+        <v>0.910239051530908</v>
       </c>
       <c r="L261" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M261" s="26">
-        <v>29.75</v>
+        <v>28</v>
       </c>
       <c r="N261" s="26"/>
       <c r="O261" s="26">
-        <v>50.83</v>
+        <v>47.84</v>
       </c>
       <c r="P261" s="26"/>
       <c r="Q261" s="26">
@@ -12311,28 +12311,28 @@
         <v>1.146</v>
       </c>
       <c r="I264" s="31">
-        <v>3.108</v>
+        <v>2.637</v>
       </c>
       <c r="J264" s="31"/>
       <c r="K264" s="31">
-        <v>2.71204188481675</v>
+        <v>2.30104712041885</v>
       </c>
       <c r="L264" s="31" t="s">
         <v>55</v>
       </c>
       <c r="M264" s="31">
-        <v>10.878</v>
+        <v>9.2295</v>
       </c>
       <c r="N264" s="31"/>
       <c r="O264" s="31">
-        <v>18.3372</v>
+        <v>15.5583</v>
       </c>
       <c r="P264" s="31"/>
       <c r="Q264" s="31">
         <v>40.68</v>
       </c>
       <c r="R264" s="31" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="S264" s="31">
         <v>0</v>
@@ -12692,21 +12692,21 @@
         <v>215.4835</v>
       </c>
       <c r="I277" s="26">
-        <v>109.061</v>
+        <v>92.354</v>
       </c>
       <c r="J277" s="26"/>
       <c r="K277" s="26">
-        <v>0.506122278503923</v>
+        <v>0.428589659997169</v>
       </c>
       <c r="L277" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M277" s="26">
-        <v>399.8939687</v>
+        <v>338.6344118</v>
       </c>
       <c r="N277" s="26"/>
       <c r="O277" s="26">
-        <v>696.89979</v>
+        <v>590.14206</v>
       </c>
       <c r="P277" s="26"/>
       <c r="Q277" s="26">
@@ -12782,21 +12782,21 @@
         <v>126</v>
       </c>
       <c r="I279" s="26">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J279" s="26"/>
       <c r="K279" s="26">
-        <v>0.595238095238095</v>
+        <v>0.53968253968254</v>
       </c>
       <c r="L279" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M279" s="26">
-        <v>115.1775</v>
+        <v>104.4276</v>
       </c>
       <c r="N279" s="26"/>
       <c r="O279" s="26">
-        <v>195</v>
+        <v>176.8</v>
       </c>
       <c r="P279" s="26"/>
       <c r="Q279" s="26">
@@ -12918,21 +12918,21 @@
         <v>56.122</v>
       </c>
       <c r="I282" s="31">
-        <v>41.936</v>
+        <v>37.791</v>
       </c>
       <c r="J282" s="31"/>
       <c r="K282" s="31">
-        <v>0.747229250561277</v>
+        <v>0.673372296069278</v>
       </c>
       <c r="L282" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M282" s="31">
-        <v>167.744</v>
+        <v>151.164</v>
       </c>
       <c r="N282" s="31"/>
       <c r="O282" s="31">
-        <v>293.13264</v>
+        <v>264.15909</v>
       </c>
       <c r="P282" s="31"/>
       <c r="Q282" s="31">
@@ -13006,21 +13006,21 @@
         <v>9.0782</v>
       </c>
       <c r="I284" s="31">
-        <v>17.555</v>
+        <v>15.938</v>
       </c>
       <c r="J284" s="31"/>
       <c r="K284" s="31">
-        <v>1.93375338723535</v>
+        <v>1.75563437685885</v>
       </c>
       <c r="L284" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M284" s="31">
-        <v>70.22</v>
+        <v>63.752</v>
       </c>
       <c r="N284" s="31"/>
       <c r="O284" s="31">
-        <v>122.70945</v>
+        <v>111.40662</v>
       </c>
       <c r="P284" s="31"/>
       <c r="Q284" s="31">
@@ -13050,21 +13050,21 @@
         <v>27.9249</v>
       </c>
       <c r="I285" s="26">
-        <v>20.423</v>
+        <v>19.807</v>
       </c>
       <c r="J285" s="26"/>
       <c r="K285" s="26">
-        <v>0.731354454268413</v>
+        <v>0.709295288434336</v>
       </c>
       <c r="L285" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M285" s="26">
-        <v>85.0965141</v>
+        <v>82.5298269</v>
       </c>
       <c r="N285" s="26"/>
       <c r="O285" s="26">
-        <v>142.75677</v>
+        <v>138.45093</v>
       </c>
       <c r="P285" s="26"/>
       <c r="Q285" s="26">
@@ -13094,28 +13094,28 @@
         <v>2636</v>
       </c>
       <c r="I286" s="31">
-        <v>-1684</v>
+        <v>-3587</v>
       </c>
       <c r="J286" s="31"/>
       <c r="K286" s="31">
-        <v>-0.638846737481032</v>
+        <v>-1.36077389984826</v>
       </c>
       <c r="L286" s="31" t="s">
         <v>84</v>
       </c>
       <c r="M286" s="31">
-        <v>-6.3992</v>
+        <v>-13.6306</v>
       </c>
       <c r="N286" s="31"/>
       <c r="O286" s="31">
-        <v>-10.08716</v>
+        <v>-21.48613</v>
       </c>
       <c r="P286" s="31"/>
       <c r="Q286" s="31">
         <v>36.56</v>
       </c>
       <c r="R286" s="31" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="S286" s="31">
         <v>0</v>
@@ -13138,21 +13138,21 @@
         <v>0.6222</v>
       </c>
       <c r="I287" s="26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J287" s="26"/>
       <c r="K287" s="26">
-        <v>22.5008036001286</v>
+        <v>19.2864030858245</v>
       </c>
       <c r="L287" s="26" t="s">
         <v>55</v>
       </c>
       <c r="M287" s="26">
-        <v>47.6</v>
+        <v>40.8</v>
       </c>
       <c r="N287" s="26"/>
       <c r="O287" s="26">
-        <v>79.66</v>
+        <v>68.28</v>
       </c>
       <c r="P287" s="26"/>
       <c r="Q287" s="26">
@@ -13514,22 +13514,22 @@
       </c>
       <c r="G300" s="59"/>
       <c r="H300" s="60">
-        <v>-4217463.802</v>
+        <v>-4222942.856</v>
       </c>
       <c r="I300" s="60"/>
       <c r="J300" s="60"/>
       <c r="K300" s="60">
-        <v>-39831.5795897967</v>
+        <v>-40189.4536818967</v>
       </c>
       <c r="L300" s="60"/>
       <c r="M300" s="60"/>
       <c r="N300" s="60"/>
       <c r="O300" s="60">
-        <v>-92254.4510150663</v>
+        <v>-92850.0564650663</v>
       </c>
       <c r="P300" s="60"/>
       <c r="Q300" s="60">
-        <v>56.8242191552452</v>
+        <v>56.7157466436033</v>
       </c>
       <c r="R300" s="60">
         <v>0</v>
@@ -13550,22 +13550,22 @@
       </c>
       <c r="G301" s="66"/>
       <c r="H301" s="67">
-        <v>-4217463.802</v>
+        <v>-4222942.856</v>
       </c>
       <c r="I301" s="68"/>
       <c r="J301" s="68"/>
       <c r="K301" s="67">
-        <v>-39831.5795897967</v>
+        <v>-40189.4536818967</v>
       </c>
       <c r="L301" s="68"/>
       <c r="M301" s="68"/>
       <c r="N301" s="68"/>
       <c r="O301" s="67">
-        <v>-92254.4510150663</v>
+        <v>-92850.0564650663</v>
       </c>
       <c r="P301" s="68"/>
       <c r="Q301" s="67">
-        <v>56.8242191552452</v>
+        <v>56.7157466436033</v>
       </c>
       <c r="R301" s="67">
         <v>0</v>

--- a/03_model/inputs/stock_on_hand_2026-05-13.xlsx
+++ b/03_model/inputs/stock_on_hand_2026-05-13.xlsx
@@ -246,7 +246,7 @@
     <t>1 of 12</t>
   </si>
   <si>
-    <t>Generated 13/05/2026 at 16:05:01</t>
+    <t>Generated 13/05/2026 at 16:36:00</t>
   </si>
   <si>
     <t>9313711001015</t>
@@ -2651,21 +2651,21 @@
         <v>140.5392</v>
       </c>
       <c r="I10" s="26">
-        <v>51.681</v>
+        <v>47.73</v>
       </c>
       <c r="J10" s="26"/>
       <c r="K10" s="26">
-        <v>0.367733699921445</v>
+        <v>0.339620547149834</v>
       </c>
       <c r="L10" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M10" s="26">
-        <v>77.5215</v>
+        <v>71.595</v>
       </c>
       <c r="N10" s="26"/>
       <c r="O10" s="26">
-        <v>139.02189</v>
+        <v>128.3937</v>
       </c>
       <c r="P10" s="26"/>
       <c r="Q10" s="26">
@@ -2741,21 +2741,21 @@
         <v>30.9767</v>
       </c>
       <c r="I12" s="26">
-        <v>17.975</v>
+        <v>17.409</v>
       </c>
       <c r="J12" s="26"/>
       <c r="K12" s="26">
-        <v>0.580274851743407</v>
+        <v>0.56200305390826</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M12" s="26">
-        <v>98.8625</v>
+        <v>95.7495</v>
       </c>
       <c r="N12" s="26"/>
       <c r="O12" s="26">
-        <v>165.19025</v>
+        <v>159.98871</v>
       </c>
       <c r="P12" s="26"/>
       <c r="Q12" s="26">
@@ -3615,21 +3615,21 @@
         <v>132.2222</v>
       </c>
       <c r="I35" s="26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J35" s="26"/>
       <c r="K35" s="26">
-        <v>0.128571450180076</v>
+        <v>0.113445397217714</v>
       </c>
       <c r="L35" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M35" s="26">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="N35" s="26"/>
       <c r="O35" s="26">
-        <v>113.73</v>
+        <v>100.35</v>
       </c>
       <c r="P35" s="26"/>
       <c r="Q35" s="26">
@@ -4908,21 +4908,21 @@
         <v>66.1111</v>
       </c>
       <c r="I68" s="31">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J68" s="31"/>
       <c r="K68" s="31">
-        <v>0.181512635548342</v>
+        <v>0.136134476661257</v>
       </c>
       <c r="L68" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M68" s="31">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="N68" s="31"/>
       <c r="O68" s="31">
-        <v>47.88</v>
+        <v>35.91</v>
       </c>
       <c r="P68" s="31"/>
       <c r="Q68" s="31">
@@ -5046,21 +5046,21 @@
         <v>41.8732</v>
       </c>
       <c r="I71" s="26">
-        <v>11.669</v>
+        <v>10.918</v>
       </c>
       <c r="J71" s="26"/>
       <c r="K71" s="26">
-        <v>0.278674665418454</v>
+        <v>0.260739566118663</v>
       </c>
       <c r="L71" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M71" s="26">
-        <v>23.338</v>
+        <v>21.836</v>
       </c>
       <c r="N71" s="26"/>
       <c r="O71" s="26">
-        <v>58.22831</v>
+        <v>54.48082</v>
       </c>
       <c r="P71" s="26"/>
       <c r="Q71" s="26">
@@ -5138,21 +5138,21 @@
         <v>33.9631</v>
       </c>
       <c r="I73" s="26">
-        <v>25.14</v>
+        <v>24.394</v>
       </c>
       <c r="J73" s="26"/>
       <c r="K73" s="26">
-        <v>0.740215115816872</v>
+        <v>0.71825010084474</v>
       </c>
       <c r="L73" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M73" s="26">
-        <v>100.56</v>
+        <v>97.576</v>
       </c>
       <c r="N73" s="26"/>
       <c r="O73" s="26">
-        <v>175.7286</v>
+        <v>170.51406</v>
       </c>
       <c r="P73" s="26"/>
       <c r="Q73" s="26">
@@ -5182,21 +5182,21 @@
         <v>7.3889</v>
       </c>
       <c r="I74" s="31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J74" s="31"/>
       <c r="K74" s="31">
-        <v>0.947366996440607</v>
+        <v>0.812028854091949</v>
       </c>
       <c r="L74" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M74" s="31">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="N74" s="31"/>
       <c r="O74" s="31">
-        <v>31.5</v>
+        <v>27</v>
       </c>
       <c r="P74" s="31"/>
       <c r="Q74" s="31">
@@ -5517,21 +5517,21 @@
         <v>18.9778</v>
       </c>
       <c r="I86" s="31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J86" s="31"/>
       <c r="K86" s="31">
-        <v>0.421545173834691</v>
+        <v>0.368852027105355</v>
       </c>
       <c r="L86" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M86" s="31">
-        <v>68</v>
+        <v>59.5</v>
       </c>
       <c r="N86" s="31"/>
       <c r="O86" s="31">
-        <v>127.92</v>
+        <v>111.93</v>
       </c>
       <c r="P86" s="31"/>
       <c r="Q86" s="31">
@@ -5831,21 +5831,21 @@
         <v>14.6057</v>
       </c>
       <c r="I93" s="26">
-        <v>20.767</v>
+        <v>20.176</v>
       </c>
       <c r="J93" s="26"/>
       <c r="K93" s="26">
-        <v>1.42184215751385</v>
+        <v>1.38137850291325</v>
       </c>
       <c r="L93" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M93" s="26">
-        <v>62.301</v>
+        <v>60.528</v>
       </c>
       <c r="N93" s="26"/>
       <c r="O93" s="26">
-        <v>114.01083</v>
+        <v>110.76624</v>
       </c>
       <c r="P93" s="26"/>
       <c r="Q93" s="26">
@@ -6363,21 +6363,21 @@
         <v>17.3444</v>
       </c>
       <c r="I105" s="26">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J105" s="26"/>
       <c r="K105" s="26">
-        <v>1.61435391250202</v>
+        <v>1.55669841562695</v>
       </c>
       <c r="L105" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M105" s="26">
-        <v>156.8</v>
+        <v>151.2</v>
       </c>
       <c r="N105" s="26"/>
       <c r="O105" s="26">
-        <v>165.2</v>
+        <v>159.3</v>
       </c>
       <c r="P105" s="26"/>
       <c r="Q105" s="26">
@@ -6836,21 +6836,21 @@
         <v>33.3462</v>
       </c>
       <c r="I120" s="31">
-        <v>39.989</v>
+        <v>39.773</v>
       </c>
       <c r="J120" s="31"/>
       <c r="K120" s="31">
-        <v>1.19920710605706</v>
+        <v>1.19272960637194</v>
       </c>
       <c r="L120" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M120" s="31">
-        <v>79.978</v>
+        <v>79.546</v>
       </c>
       <c r="N120" s="31"/>
       <c r="O120" s="31">
-        <v>159.55611</v>
+        <v>158.69427</v>
       </c>
       <c r="P120" s="31"/>
       <c r="Q120" s="31">
@@ -7667,21 +7667,21 @@
         <v>5937.5</v>
       </c>
       <c r="I143" s="26">
-        <v>-10855.5</v>
+        <v>-11676.5</v>
       </c>
       <c r="J143" s="26"/>
       <c r="K143" s="26">
-        <v>-1.82829473684211</v>
+        <v>-1.96656842105263</v>
       </c>
       <c r="L143" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M143" s="26">
-        <v>-43.422</v>
+        <v>-46.706</v>
       </c>
       <c r="N143" s="26"/>
       <c r="O143" s="26">
-        <v>-75.879945</v>
+        <v>-81.618735</v>
       </c>
       <c r="P143" s="26"/>
       <c r="Q143" s="26">
@@ -8552,21 +8552,21 @@
         <v>127.4</v>
       </c>
       <c r="I167" s="26">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J167" s="26"/>
       <c r="K167" s="26">
-        <v>0.745682888540031</v>
+        <v>0.722135007849294</v>
       </c>
       <c r="L167" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M167" s="26">
-        <v>221.6635</v>
+        <v>214.6636</v>
       </c>
       <c r="N167" s="26"/>
       <c r="O167" s="26">
-        <v>379.05</v>
+        <v>367.08</v>
       </c>
       <c r="P167" s="26"/>
       <c r="Q167" s="26">
@@ -8642,21 +8642,21 @@
         <v>8.5746</v>
       </c>
       <c r="I169" s="26">
-        <v>21.917</v>
+        <v>21.016</v>
       </c>
       <c r="J169" s="26"/>
       <c r="K169" s="26">
-        <v>2.55603759942155</v>
+        <v>2.4509598115364</v>
       </c>
       <c r="L169" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M169" s="26">
-        <v>84.7464639</v>
+        <v>81.2625672</v>
       </c>
       <c r="N169" s="26"/>
       <c r="O169" s="26">
-        <v>144.43303</v>
+        <v>138.49544</v>
       </c>
       <c r="P169" s="26"/>
       <c r="Q169" s="26">
@@ -9354,28 +9354,28 @@
         <v>23.6444</v>
       </c>
       <c r="I185" s="26">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="J185" s="26"/>
       <c r="K185" s="26">
-        <v>-6.97839657593341</v>
+        <v>-7.02068988851483</v>
       </c>
       <c r="L185" s="26" t="s">
         <v>70</v>
       </c>
       <c r="M185" s="26">
-        <v>-429</v>
+        <v>-431.6</v>
       </c>
       <c r="N185" s="26"/>
       <c r="O185" s="26">
-        <v>-707.85</v>
+        <v>-712.14</v>
       </c>
       <c r="P185" s="26"/>
       <c r="Q185" s="26">
         <v>39.39</v>
       </c>
       <c r="R185" s="26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S185" s="26">
         <v>0</v>
@@ -9555,21 +9555,21 @@
         <v>76.4591</v>
       </c>
       <c r="I194" s="45">
-        <v>50.77</v>
+        <v>48.25</v>
       </c>
       <c r="J194" s="45"/>
       <c r="K194" s="45">
-        <v>0.664015140120666</v>
+        <v>0.631056342541306</v>
       </c>
       <c r="L194" s="45" t="s">
         <v>22</v>
       </c>
       <c r="M194" s="45">
-        <v>228.465</v>
+        <v>217.125</v>
       </c>
       <c r="N194" s="45"/>
       <c r="O194" s="45">
-        <v>385.3443</v>
+        <v>366.2175</v>
       </c>
       <c r="P194" s="45"/>
       <c r="Q194" s="45">
@@ -9823,21 +9823,21 @@
         <v>1750.7</v>
       </c>
       <c r="I200" s="31">
-        <v>-438.8</v>
+        <v>-529.8</v>
       </c>
       <c r="J200" s="31"/>
       <c r="K200" s="31">
-        <v>-0.250642600102816</v>
+        <v>-0.302621808419489</v>
       </c>
       <c r="L200" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M200" s="31">
-        <v>-8.3372</v>
+        <v>-10.0662</v>
       </c>
       <c r="N200" s="31"/>
       <c r="O200" s="31">
-        <v>-11.404412</v>
+        <v>-13.769502</v>
       </c>
       <c r="P200" s="31"/>
       <c r="Q200" s="31">
@@ -10181,21 +10181,21 @@
         <v>129.8889</v>
       </c>
       <c r="I208" s="31">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J208" s="31"/>
       <c r="K208" s="31">
-        <v>0.58511543326643</v>
+        <v>0.562018771426966</v>
       </c>
       <c r="L208" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M208" s="31">
-        <v>88.6692</v>
+        <v>85.1691</v>
       </c>
       <c r="N208" s="31"/>
       <c r="O208" s="31">
-        <v>151.24</v>
+        <v>145.27</v>
       </c>
       <c r="P208" s="31"/>
       <c r="Q208" s="31">
@@ -11214,21 +11214,21 @@
         <v>96.8333</v>
       </c>
       <c r="I235" s="26">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J235" s="26"/>
       <c r="K235" s="26">
-        <v>0.609294529877635</v>
+        <v>0.598967503947506</v>
       </c>
       <c r="L235" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M235" s="26">
-        <v>67.85</v>
+        <v>66.7</v>
       </c>
       <c r="N235" s="26"/>
       <c r="O235" s="26">
-        <v>126.85</v>
+        <v>124.7</v>
       </c>
       <c r="P235" s="26"/>
       <c r="Q235" s="26">
@@ -11260,21 +11260,21 @@
         <v>23.1257</v>
       </c>
       <c r="I236" s="31">
-        <v>7.4</v>
+        <v>7.174</v>
       </c>
       <c r="J236" s="31"/>
       <c r="K236" s="31">
-        <v>0.319990313806717</v>
+        <v>0.310217636655323</v>
       </c>
       <c r="L236" s="31" t="s">
         <v>22</v>
       </c>
       <c r="M236" s="31">
-        <v>40.7</v>
+        <v>39.457</v>
       </c>
       <c r="N236" s="31"/>
       <c r="O236" s="31">
-        <v>70.966</v>
+        <v>68.79866</v>
       </c>
       <c r="P236" s="31"/>
       <c r="Q236" s="31">
@@ -11869,28 +11869,28 @@
         <v>18.9</v>
       </c>
       <c r="I254" s="31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J254" s="31"/>
       <c r="K254" s="31">
-        <v>0.105820105820106</v>
+        <v>0.0529100529100529</v>
       </c>
       <c r="L254" s="31" t="s">
         <v>55</v>
       </c>
       <c r="M254" s="31">
-        <v>5.3334</v>
+        <v>2.6667</v>
       </c>
       <c r="N254" s="31"/>
       <c r="O254" s="31">
-        <v>9.18</v>
+        <v>4.59</v>
       </c>
       <c r="P254" s="31"/>
       <c r="Q254" s="31">
         <v>41.9</v>
       </c>
       <c r="R254" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S254" s="31">
         <v>0</v>
@@ -12179,21 +12179,21 @@
         <v>17.5778</v>
       </c>
       <c r="I261" s="26">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J261" s="26"/>
       <c r="K261" s="26">
-        <v>0.910239051530908</v>
+        <v>0.853349110810227</v>
       </c>
       <c r="L261" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M261" s="26">
-        <v>28</v>
+        <v>26.25</v>
       </c>
       <c r="N261" s="26"/>
       <c r="O261" s="26">
-        <v>47.84</v>
+        <v>44.85</v>
       </c>
       <c r="P261" s="26"/>
       <c r="Q261" s="26">
@@ -12692,21 +12692,21 @@
         <v>215.4835</v>
       </c>
       <c r="I277" s="26">
-        <v>92.354</v>
+        <v>87.573</v>
       </c>
       <c r="J277" s="26"/>
       <c r="K277" s="26">
-        <v>0.428589659997169</v>
+        <v>0.406402346351345</v>
       </c>
       <c r="L277" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M277" s="26">
-        <v>338.6344118</v>
+        <v>321.1039191</v>
       </c>
       <c r="N277" s="26"/>
       <c r="O277" s="26">
-        <v>590.14206</v>
+        <v>559.59147</v>
       </c>
       <c r="P277" s="26"/>
       <c r="Q277" s="26">
@@ -12782,21 +12782,21 @@
         <v>126</v>
       </c>
       <c r="I279" s="26">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J279" s="26"/>
       <c r="K279" s="26">
-        <v>0.53968253968254</v>
+        <v>0.515873015873016</v>
       </c>
       <c r="L279" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M279" s="26">
-        <v>104.4276</v>
+        <v>99.8205</v>
       </c>
       <c r="N279" s="26"/>
       <c r="O279" s="26">
-        <v>176.8</v>
+        <v>169</v>
       </c>
       <c r="P279" s="26"/>
       <c r="Q279" s="26">
@@ -13050,21 +13050,21 @@
         <v>27.9249</v>
       </c>
       <c r="I285" s="26">
-        <v>19.807</v>
+        <v>17.563</v>
       </c>
       <c r="J285" s="26"/>
       <c r="K285" s="26">
-        <v>0.709295288434336</v>
+        <v>0.628936898610201</v>
       </c>
       <c r="L285" s="26" t="s">
         <v>22</v>
       </c>
       <c r="M285" s="26">
-        <v>82.5298269</v>
+        <v>73.1797521</v>
       </c>
       <c r="N285" s="26"/>
       <c r="O285" s="26">
-        <v>138.45093</v>
+        <v>122.76537</v>
       </c>
       <c r="P285" s="26"/>
       <c r="Q285" s="26">
@@ -13514,22 +13514,22 @@
       </c>
       <c r="G300" s="59"/>
       <c r="H300" s="60">
-        <v>-4222942.856</v>
+        <v>-4223893.349</v>
       </c>
       <c r="I300" s="60"/>
       <c r="J300" s="60"/>
       <c r="K300" s="60">
-        <v>-40189.4536818967</v>
+        <v>-40311.5184460967</v>
       </c>
       <c r="L300" s="60"/>
       <c r="M300" s="60"/>
       <c r="N300" s="60"/>
       <c r="O300" s="60">
-        <v>-92850.0564650663</v>
+        <v>-93052.0264150663</v>
       </c>
       <c r="P300" s="60"/>
       <c r="Q300" s="60">
-        <v>56.7157466436033</v>
+        <v>56.6785163105596</v>
       </c>
       <c r="R300" s="60">
         <v>0</v>
@@ -13550,22 +13550,22 @@
       </c>
       <c r="G301" s="66"/>
       <c r="H301" s="67">
-        <v>-4222942.856</v>
+        <v>-4223893.349</v>
       </c>
       <c r="I301" s="68"/>
       <c r="J301" s="68"/>
       <c r="K301" s="67">
-        <v>-40189.4536818967</v>
+        <v>-40311.5184460967</v>
       </c>
       <c r="L301" s="68"/>
       <c r="M301" s="68"/>
       <c r="N301" s="68"/>
       <c r="O301" s="67">
-        <v>-92850.0564650663</v>
+        <v>-93052.0264150663</v>
       </c>
       <c r="P301" s="68"/>
       <c r="Q301" s="67">
-        <v>56.7157466436033</v>
+        <v>56.6785163105596</v>
       </c>
       <c r="R301" s="67">
         <v>0</v>
